--- a/hira_material_automation/output/monthly/202601_202604__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T21:37:47</t>
+          <t>2026-04-14T21:55:46</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>785a6451b68d20fd99fb97e2be5094009322cd89c134776776edeae5901b331b</t>
+          <t>8e70a70e01b9fd5d0f2c384de7a95c691a1ff78f4c612a66751ef9df24797ea6</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T21:55:46</t>
+          <t>2026-04-24T21:53:56</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8e70a70e01b9fd5d0f2c384de7a95c691a1ff78f4c612a66751ef9df24797ea6</t>
+          <t>e687554fe3be8b8f2faf89a8b77faa9fcdb78775c6a1431c860c47ac80a9ba62</t>
         </is>
       </c>
     </row>
